--- a/src/app/modules/dashboard/excel_files/whole-plant-based-fruit-dishes.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-plant-based-fruit-dishes.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'snacks', 'desserts', 'salads']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
